--- a/fpga/projects/bad_timing2.xlsx
+++ b/fpga/projects/bad_timing2.xlsx
@@ -59,10 +59,10 @@
     <t>Path 21</t>
   </si>
   <si>
-    <t>i_system_wrapper/system_i/lte_phy_processing_0/inst/u_system_lte_bd/u_lte_pss_detector/u_lte_phy_pss_corr/gen_corr_lane[0].gen_corr_pss[0].corr_re_reg[0][0][47]_replica/C</t>
-  </si>
-  <si>
-    <t>i_system_wrapper/system_i/lte_phy_processing_0/inst/u_system_lte_bd/u_lte_pss_detector/u_lte_phy_pss_corr/o_dbg_mag_pss0_reg[18]/D</t>
+    <t>i_system_wrapper/system_i/lte_phy_processing_0/inst/u_system_lte_bd/u_lte_pss_detector/u_lte_phy_pss_corr/frame_best_mag_reg[10]/C</t>
+  </si>
+  <si>
+    <t>i_system_wrapper/system_i/lte_phy_processing_0/inst/u_system_lte_bd/u_lte_pss_detector/u_lte_phy_pss_corr/o_dbg_mag_pss2_reg[20]/D</t>
   </si>
   <si>
     <t>clk_div_sel_1_s</t>
@@ -74,55 +74,55 @@
     <t>Path 22</t>
   </si>
   <si>
-    <t>i_system_wrapper/system_i/lte_phy_processing_0/inst/u_system_lte_bd/u_lte_pss_detector/u_lte_phy_pss_corr/o_dbg_mag_pss2_reg[20]/D</t>
+    <t>i_system_wrapper/system_i/lte_phy_processing_0/inst/u_system_lte_bd/u_lte_pss_detector/u_lte_phy_pss_corr/frame_best_mag2_reg[4]/D</t>
   </si>
   <si>
     <t>Path 23</t>
   </si>
   <si>
-    <t>i_system_wrapper/system_i/lte_phy_processing_0/inst/u_system_lte_bd/u_lte_pss_detector/u_lte_phy_pss_corr/o_dbg_mag_pss2_reg[27]/D</t>
+    <t>i_system_wrapper/system_i/lte_phy_processing_0/inst/u_system_lte_bd/u_lte_pss_detector/u_lte_phy_pss_corr/o_dbg_mag_pss2_reg[21]/D</t>
   </si>
   <si>
     <t>Path 24</t>
   </si>
   <si>
-    <t>i_system_wrapper/system_i/lte_phy_processing_0/inst/u_system_lte_bd/u_lte_pss_detector/u_lte_phy_pss_corr/o_dbg_mag_pss1_reg[12]/D</t>
+    <t>i_system_wrapper/system_i/lte_phy_processing_0/inst/u_system_lte_bd/u_lte_pss_detector/u_lte_phy_pss_corr/o_dbg_mag_pss2_reg[25]/D</t>
   </si>
   <si>
     <t>Path 25</t>
   </si>
   <si>
-    <t>i_system_wrapper/system_i/lte_phy_processing_0/inst/u_system_lte_bd/u_lte_pss_detector/u_lte_phy_pss_corr/o_dbg_mag_pss1_reg[14]/D</t>
+    <t>i_system_wrapper/system_i/lte_phy_processing_0/inst/u_system_lte_bd/u_lte_pss_detector/u_lte_phy_pss_corr/frame_best_mag2_reg[12]/D</t>
   </si>
   <si>
     <t>Path 26</t>
   </si>
   <si>
-    <t>i_system_wrapper/system_i/lte_phy_processing_0/inst/u_system_lte_bd/u_lte_pss_detector/u_lte_phy_pss_corr/o_dbg_mag_pss2_reg[16]/CE</t>
+    <t>i_system_wrapper/system_i/lte_phy_processing_0/inst/u_system_lte_bd/u_lte_pss_detector/u_lte_phy_pss_corr/o_dbg_mag_pss1_reg[0]/D</t>
   </si>
   <si>
     <t>Path 27</t>
   </si>
   <si>
-    <t>i_system_wrapper/system_i/lte_phy_processing_0/inst/u_system_lte_bd/u_lte_pss_detector/u_lte_phy_pss_corr/o_shift_reg[12]/CE</t>
+    <t>i_system_wrapper/system_i/lte_phy_processing_0/inst/u_system_lte_bd/u_lte_pss_detector/u_lte_phy_pss_corr/frame_best_mag1_reg[3]/D</t>
   </si>
   <si>
     <t>Path 28</t>
   </si>
   <si>
-    <t>i_system_wrapper/system_i/lte_phy_processing_0/inst/u_system_lte_bd/u_lte_pss_detector/u_lte_phy_pss_corr/o_shift_reg[7]/CE</t>
+    <t>i_system_wrapper/system_i/lte_phy_processing_0/inst/u_system_lte_bd/u_lte_pss_detector/u_lte_phy_pss_corr/o_dbg_mag_pss0_reg[1]/D</t>
   </si>
   <si>
     <t>Path 29</t>
   </si>
   <si>
-    <t>i_system_wrapper/system_i/lte_phy_processing_0/inst/u_system_lte_bd/u_lte_pss_detector/u_lte_phy_pss_corr/o_shift_reg[8]/CE</t>
+    <t>i_system_wrapper/system_i/lte_phy_processing_0/inst/u_system_lte_bd/u_lte_pss_detector/u_lte_phy_pss_corr/o_dbg_mag_pss1_reg[32]/D</t>
   </si>
   <si>
     <t>Path 30</t>
   </si>
   <si>
-    <t>i_system_wrapper/system_i/lte_phy_processing_0/inst/u_system_lte_bd/u_lte_pss_detector/u_lte_phy_pss_corr/o_dbg_mag_pss2_reg[24]/D</t>
+    <t>i_system_wrapper/system_i/lte_phy_processing_0/inst/u_system_lte_bd/u_lte_pss_detector/u_lte_phy_pss_corr/frame_best_mag2_reg[22]/D</t>
   </si>
 </sst>
 </file>
@@ -264,13 +264,13 @@
         <v>14</v>
       </c>
       <c r="B2" t="n" s="4">
-        <v>-38.527000427246094</v>
+        <v>-29.60700035095215</v>
       </c>
       <c r="C2" t="n" s="6">
-        <v>86.0</v>
+        <v>72.0</v>
       </c>
       <c r="D2" t="n" s="6">
-        <v>204.0</v>
+        <v>191.0</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>15</v>
@@ -279,13 +279,13 @@
         <v>16</v>
       </c>
       <c r="G2" t="n" s="4">
-        <v>46.355953216552734</v>
+        <v>37.583717346191406</v>
       </c>
       <c r="H2" t="n" s="4">
-        <v>19.13100242614746</v>
+        <v>15.344006538391113</v>
       </c>
       <c r="I2" t="n" s="4">
-        <v>27.224952697753906</v>
+        <v>22.23971176147461</v>
       </c>
       <c r="J2" t="n" s="4">
         <v>8.0</v>
@@ -308,13 +308,13 @@
         <v>19</v>
       </c>
       <c r="B3" t="n" s="4">
-        <v>-38.415000915527344</v>
+        <v>-29.510000228881836</v>
       </c>
       <c r="C3" t="n" s="6">
-        <v>86.0</v>
+        <v>72.0</v>
       </c>
       <c r="D3" t="n" s="6">
-        <v>204.0</v>
+        <v>191.0</v>
       </c>
       <c r="E3" t="s" s="2">
         <v>15</v>
@@ -323,13 +323,13 @@
         <v>20</v>
       </c>
       <c r="G3" t="n" s="4">
-        <v>46.24087142944336</v>
+        <v>37.443058013916016</v>
       </c>
       <c r="H3" t="n" s="4">
-        <v>19.13100242614746</v>
+        <v>15.344006538391113</v>
       </c>
       <c r="I3" t="n" s="4">
-        <v>27.1098690032959</v>
+        <v>22.09905242919922</v>
       </c>
       <c r="J3" t="n" s="4">
         <v>8.0</v>
@@ -352,13 +352,13 @@
         <v>21</v>
       </c>
       <c r="B4" t="n" s="4">
-        <v>-38.4119987487793</v>
+        <v>-29.506000518798828</v>
       </c>
       <c r="C4" t="n" s="6">
-        <v>86.0</v>
+        <v>72.0</v>
       </c>
       <c r="D4" t="n" s="6">
-        <v>204.0</v>
+        <v>191.0</v>
       </c>
       <c r="E4" t="s" s="2">
         <v>15</v>
@@ -367,13 +367,13 @@
         <v>22</v>
       </c>
       <c r="G4" t="n" s="4">
-        <v>46.20859146118164</v>
+        <v>37.43520736694336</v>
       </c>
       <c r="H4" t="n" s="4">
-        <v>19.13100242614746</v>
+        <v>15.344006538391113</v>
       </c>
       <c r="I4" t="n" s="4">
-        <v>27.07758903503418</v>
+        <v>22.091201782226562</v>
       </c>
       <c r="J4" t="n" s="4">
         <v>8.0</v>
@@ -396,13 +396,13 @@
         <v>23</v>
       </c>
       <c r="B5" t="n" s="4">
-        <v>-38.39699935913086</v>
+        <v>-29.496999740600586</v>
       </c>
       <c r="C5" t="n" s="6">
-        <v>86.0</v>
+        <v>72.0</v>
       </c>
       <c r="D5" t="n" s="6">
-        <v>204.0</v>
+        <v>191.0</v>
       </c>
       <c r="E5" t="s" s="2">
         <v>15</v>
@@ -411,13 +411,13 @@
         <v>24</v>
       </c>
       <c r="G5" t="n" s="4">
-        <v>46.20893096923828</v>
+        <v>37.47406768798828</v>
       </c>
       <c r="H5" t="n" s="4">
-        <v>19.13100242614746</v>
+        <v>15.344006538391113</v>
       </c>
       <c r="I5" t="n" s="4">
-        <v>27.077932357788086</v>
+        <v>22.13006019592285</v>
       </c>
       <c r="J5" t="n" s="4">
         <v>8.0</v>
@@ -440,13 +440,13 @@
         <v>25</v>
       </c>
       <c r="B6" t="n" s="4">
-        <v>-38.375</v>
+        <v>-29.493999481201172</v>
       </c>
       <c r="C6" t="n" s="6">
-        <v>86.0</v>
+        <v>72.0</v>
       </c>
       <c r="D6" t="n" s="6">
-        <v>204.0</v>
+        <v>191.0</v>
       </c>
       <c r="E6" t="s" s="2">
         <v>15</v>
@@ -455,13 +455,13 @@
         <v>26</v>
       </c>
       <c r="G6" t="n" s="4">
-        <v>46.3365478515625</v>
+        <v>37.29743194580078</v>
       </c>
       <c r="H6" t="n" s="4">
-        <v>19.13100242614746</v>
+        <v>15.344006538391113</v>
       </c>
       <c r="I6" t="n" s="4">
-        <v>27.205547332763672</v>
+        <v>21.953426361083984</v>
       </c>
       <c r="J6" t="n" s="4">
         <v>8.0</v>
@@ -484,13 +484,13 @@
         <v>27</v>
       </c>
       <c r="B7" t="n" s="4">
-        <v>-38.37099838256836</v>
+        <v>-29.482999801635742</v>
       </c>
       <c r="C7" t="n" s="6">
-        <v>85.0</v>
+        <v>72.0</v>
       </c>
       <c r="D7" t="n" s="6">
-        <v>164.0</v>
+        <v>191.0</v>
       </c>
       <c r="E7" t="s" s="2">
         <v>15</v>
@@ -499,13 +499,13 @@
         <v>28</v>
       </c>
       <c r="G7" t="n" s="4">
-        <v>46.008384704589844</v>
+        <v>37.4149284362793</v>
       </c>
       <c r="H7" t="n" s="4">
-        <v>19.007001876831055</v>
+        <v>15.344006538391113</v>
       </c>
       <c r="I7" t="n" s="4">
-        <v>27.001380920410156</v>
+        <v>22.0709228515625</v>
       </c>
       <c r="J7" t="n" s="4">
         <v>8.0</v>
@@ -528,13 +528,13 @@
         <v>29</v>
       </c>
       <c r="B8" t="n" s="4">
-        <v>-38.37099838256836</v>
+        <v>-29.47599983215332</v>
       </c>
       <c r="C8" t="n" s="6">
-        <v>85.0</v>
+        <v>72.0</v>
       </c>
       <c r="D8" t="n" s="6">
-        <v>164.0</v>
+        <v>191.0</v>
       </c>
       <c r="E8" t="s" s="2">
         <v>15</v>
@@ -543,13 +543,13 @@
         <v>30</v>
       </c>
       <c r="G8" t="n" s="4">
-        <v>46.008384704589844</v>
+        <v>37.45331954956055</v>
       </c>
       <c r="H8" t="n" s="4">
-        <v>19.007001876831055</v>
+        <v>15.344006538391113</v>
       </c>
       <c r="I8" t="n" s="4">
-        <v>27.001380920410156</v>
+        <v>22.109312057495117</v>
       </c>
       <c r="J8" t="n" s="4">
         <v>8.0</v>
@@ -572,13 +572,13 @@
         <v>31</v>
       </c>
       <c r="B9" t="n" s="4">
-        <v>-38.37099838256836</v>
+        <v>-29.47599983215332</v>
       </c>
       <c r="C9" t="n" s="6">
-        <v>85.0</v>
+        <v>72.0</v>
       </c>
       <c r="D9" t="n" s="6">
-        <v>164.0</v>
+        <v>191.0</v>
       </c>
       <c r="E9" t="s" s="2">
         <v>15</v>
@@ -587,13 +587,13 @@
         <v>32</v>
       </c>
       <c r="G9" t="n" s="4">
-        <v>46.008384704589844</v>
+        <v>37.44826126098633</v>
       </c>
       <c r="H9" t="n" s="4">
-        <v>19.007001876831055</v>
+        <v>15.344006538391113</v>
       </c>
       <c r="I9" t="n" s="4">
-        <v>27.001380920410156</v>
+        <v>22.1042537689209</v>
       </c>
       <c r="J9" t="n" s="4">
         <v>8.0</v>
@@ -616,13 +616,13 @@
         <v>33</v>
       </c>
       <c r="B10" t="n" s="4">
-        <v>-38.37099838256836</v>
+        <v>-29.4689998626709</v>
       </c>
       <c r="C10" t="n" s="6">
-        <v>85.0</v>
+        <v>72.0</v>
       </c>
       <c r="D10" t="n" s="6">
-        <v>164.0</v>
+        <v>191.0</v>
       </c>
       <c r="E10" t="s" s="2">
         <v>15</v>
@@ -631,13 +631,13 @@
         <v>34</v>
       </c>
       <c r="G10" t="n" s="4">
-        <v>46.008384704589844</v>
+        <v>37.44526290893555</v>
       </c>
       <c r="H10" t="n" s="4">
-        <v>19.007001876831055</v>
+        <v>15.344006538391113</v>
       </c>
       <c r="I10" t="n" s="4">
-        <v>27.001380920410156</v>
+        <v>22.101253509521484</v>
       </c>
       <c r="J10" t="n" s="4">
         <v>8.0</v>
@@ -660,13 +660,13 @@
         <v>35</v>
       </c>
       <c r="B11" t="n" s="4">
-        <v>-38.3650016784668</v>
+        <v>-29.459999084472656</v>
       </c>
       <c r="C11" t="n" s="6">
-        <v>86.0</v>
+        <v>72.0</v>
       </c>
       <c r="D11" t="n" s="6">
-        <v>204.0</v>
+        <v>191.0</v>
       </c>
       <c r="E11" t="s" s="2">
         <v>15</v>
@@ -675,13 +675,13 @@
         <v>36</v>
       </c>
       <c r="G11" t="n" s="4">
-        <v>46.19841766357422</v>
+        <v>37.392059326171875</v>
       </c>
       <c r="H11" t="n" s="4">
-        <v>19.13100242614746</v>
+        <v>15.344006538391113</v>
       </c>
       <c r="I11" t="n" s="4">
-        <v>27.067415237426758</v>
+        <v>22.048053741455078</v>
       </c>
       <c r="J11" t="n" s="4">
         <v>8.0</v>
